--- a/Verification.xlsx
+++ b/Verification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsofteur-my.sharepoint.com/personal/sheroor_microsoft_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsofteur-my.sharepoint.com/personal/lima8_microsoft_com/Documents/Fabric/FabricDataAgentDemo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC76D1FE-AE21-4DEF-846F-674A6CE98FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{CC76D1FE-AE21-4DEF-846F-674A6CE98FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EA1DF21-388E-4786-BAA5-258F81CD7D30}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{310D1B79-3D47-465E-A9CA-AF03CFB5FAB5}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="18000" windowHeight="11170" xr2:uid="{310D1B79-3D47-465E-A9CA-AF03CFB5FAB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -178,9 +178,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,7 +260,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -602,16 +602,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDDCEE68-918A-44F3-9629-F3919161D17C}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="48.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -651,7 +651,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -671,7 +671,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -691,7 +691,7 @@
         <v>123590881</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -711,7 +711,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -731,7 +731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -747,9 +747,11 @@
       <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="106.5">
+      <c r="F7" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="103.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -769,7 +771,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -777,7 +779,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -793,7 +795,7 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>1</v>
       </c>
@@ -827,7 +829,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -844,7 +846,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -861,7 +863,7 @@
         <v>123590881</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>4</v>
       </c>
@@ -878,7 +880,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>5</v>
       </c>
@@ -895,7 +897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="23.1">
+    <row r="19" spans="1:6" ht="23" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>6</v>
       </c>
@@ -915,7 +917,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="23.1">
+    <row r="20" spans="1:6" ht="23" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>7</v>
       </c>
@@ -935,7 +937,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="23.1">
+    <row r="21" spans="1:6" ht="23" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>8</v>
       </c>
@@ -952,7 +954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="61.5" customHeight="1">
+    <row r="22" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>9</v>
       </c>
@@ -969,7 +971,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>28</v>
@@ -982,91 +984,91 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1080,6 +1082,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{87867195-f2b8-4ac2-b0b6-6bb73cb33afc}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+  <clbl:label id="{87867195-f2b8-4ac2-b0b6-6bb73cb33afc}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" removed="0"/>
 </clbl:labelList>
 </file>